--- a/diseases/d209/2026-2029.xlsx
+++ b/diseases/d209/2026-2029.xlsx
@@ -1007,7 +1007,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">

--- a/diseases/d209/2026-2029.xlsx
+++ b/diseases/d209/2026-2029.xlsx
@@ -788,7 +788,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">

--- a/diseases/d209/2026-2029.xlsx
+++ b/diseases/d209/2026-2029.xlsx
@@ -778,7 +778,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>SER_US_PERINATAL_HEPATITIS_B</t>
+          <t>HOLD_US_b3179b616b70c5603c09d7d1517b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>SER_US_PERINATAL_HEPATITIS_B</t>
+          <t>HOLD_US_b3179b616b70c5603c09d7d1517b</t>
         </is>
       </c>
       <c r="AT2" t="n">
@@ -878,7 +878,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -930,34 +930,17 @@
       <c r="P3" t="n">
         <v>1</v>
       </c>
+      <c r="R3" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>SER_US_PERINATAL_HEPATITIS_B</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>SER_US_PERINATAL_HEPATITIS_B</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>Hepatitis B, perinatal, Confirmed</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>HOLD_US_b3179b616b70c5603c09d7d1517b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -965,64 +948,6 @@
           <t>weekly</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Confirmed perinatal hepatitis B series.</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN3" t="b">
-        <v>1</v>
-      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>mixed</t>
@@ -1040,7 +965,7 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>SER_US_PERINATAL_HEPATITIS_B</t>
+          <t>HOLD_US_b3179b616b70c5603c09d7d1517b</t>
         </is>
       </c>
       <c r="AT3" t="n">
@@ -1087,405 +1012,6 @@
         </is>
       </c>
       <c r="BC3" t="inlineStr">
-        <is>
-          <t>api; api</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>D209</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>perinatal-hepatitis-b</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Perinatal hepatitis B</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>D209</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Perinatal hepatitis B</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>围产期乙型肝炎</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="N4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.0002865038132769385</v>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>SER_US_PERINATAL_HEPATITIS_B</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>mixed</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>SER_US_PERINATAL_HEPATITIS_B</t>
-        </is>
-      </c>
-      <c r="AT4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>nndss_api</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>US CDC NNDSS</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>api</t>
-        </is>
-      </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>nndss_api; nhss_hiv</t>
-        </is>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr">
-        <is>
-          <t>api; api</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>D209</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>perinatal-hepatitis-b</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Perinatal hepatitis B</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>D209</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Perinatal hepatitis B</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>围产期乙型肝炎</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="N5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>SER_US_PERINATAL_HEPATITIS_B</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>SER_US_PERINATAL_HEPATITIS_B</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>Hepatitis B, perinatal, Confirmed</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Confirmed perinatal hepatitis B series.</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN5" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>mixed</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>SER_US_PERINATAL_HEPATITIS_B</t>
-        </is>
-      </c>
-      <c r="AT5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>nndss_api</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>US CDC NNDSS</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>api</t>
-        </is>
-      </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>nndss_api; nhss_hiv</t>
-        </is>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -1617,7 +1143,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1637,7 +1163,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1647,7 +1173,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">

--- a/diseases/d209/2026-2029.xlsx
+++ b/diseases/d209/2026-2029.xlsx
@@ -771,11 +771,6 @@
       <c r="R2" t="n">
         <v>0.0002865038132769385</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U2" t="inlineStr">
         <is>
           <t>HOLD_US_b3179b616b70c5603c09d7d1517b</t>
@@ -793,12 +788,7 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -809,11 +799,6 @@
       <c r="AT2" t="n">
         <v>1</v>
       </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
-      </c>
       <c r="AV2" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -933,11 +918,6 @@
       <c r="R3" t="n">
         <v>0.0002865038132769385</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U3" t="inlineStr">
         <is>
           <t>HOLD_US_b3179b616b70c5603c09d7d1517b</t>
@@ -955,12 +935,7 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -970,11 +945,6 @@
       </c>
       <c r="AT3" t="n">
         <v>1</v>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
